--- a/artfynd/A 9819-2024 artfynd.xlsx
+++ b/artfynd/A 9819-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>105935768</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607340.8617823505</v>
+        <v>607341</v>
       </c>
       <c r="R2" t="n">
-        <v>7008647.971721172</v>
+        <v>7008648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105934669</v>
+        <v>105935769</v>
       </c>
       <c r="B3" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607198.7949470349</v>
+        <v>607348</v>
       </c>
       <c r="R3" t="n">
-        <v>7008716.883970612</v>
+        <v>7008646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +848,9 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mattis Arveström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -910,16 +880,11 @@
         <v>105935770</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -951,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607306.3743277773</v>
+        <v>607307</v>
       </c>
       <c r="R4" t="n">
-        <v>7008678.446858658</v>
+        <v>7008678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +949,9 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,16 +981,11 @@
         <v>105935772</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1067,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607277.0446584523</v>
+        <v>607277</v>
       </c>
       <c r="R5" t="n">
-        <v>7008649.012734109</v>
+        <v>7008649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,19 +1050,9 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105934668</v>
+        <v>105935382</v>
       </c>
       <c r="B6" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607340.8617823505</v>
+        <v>607341</v>
       </c>
       <c r="R6" t="n">
-        <v>7008647.971721172</v>
+        <v>7008648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105935382</v>
+        <v>105934668</v>
       </c>
       <c r="B7" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607340.8617823505</v>
+        <v>607341</v>
       </c>
       <c r="R7" t="n">
-        <v>7008647.971721172</v>
+        <v>7008648</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,19 +1252,9 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105935530</v>
+        <v>105934669</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607345.0335392037</v>
+        <v>607199</v>
       </c>
       <c r="R8" t="n">
-        <v>7008644.948248707</v>
+        <v>7008717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,19 +1353,9 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,44 +1375,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mattis Arveström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105935769</v>
+        <v>105935530</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1531,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607347.7146895111</v>
+        <v>607345</v>
       </c>
       <c r="R9" t="n">
-        <v>7008645.940875678</v>
+        <v>7008645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,19 +1454,9 @@
           <t>2022-06-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 9819-2024 artfynd.xlsx
+++ b/artfynd/A 9819-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935768</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935769</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935770</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935772</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935382</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105934668</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105934669</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,8 +1520,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105935530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>